--- a/artfynd/A 51368-2025 artfynd.xlsx
+++ b/artfynd/A 51368-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127745204</v>
+        <v>127745009</v>
       </c>
       <c r="B2" t="n">
-        <v>58552</v>
+        <v>58829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,24 +686,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>adult</t>
@@ -711,12 +720,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -755,12 +764,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,11 +779,11 @@
         <v>0</v>
       </c>
       <c r="AG2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Öppen fastmark - med eller utan enstaka träd</t>
+          <t>Vattendrag</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,57 +801,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127745009</v>
+        <v>127811130</v>
       </c>
       <c r="B3" t="n">
-        <v>58555</v>
+        <v>9596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100141</v>
+        <v>101479</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Osmoderma eremita</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428669</v>
+        <v>428767</v>
       </c>
       <c r="R3" t="n">
-        <v>6177731</v>
+        <v>6177736</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,12 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,11 +896,11 @@
         <v>0</v>
       </c>
       <c r="AG3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Vattendrag</t>
+          <t>Lövträd</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -915,6 +915,244 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127745138</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Syremöllan, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>428669</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6177731</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sjöbo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fränninge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Josefine Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Josefine Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127832791</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99026</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219788</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Syremöllan, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>428754</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6177714</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sjöbo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fränninge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Josefine Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Josefine Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
